--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC4D4D92-A36B-4CB3-80B0-4BF54638EB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63A1A4F-9E1A-45C8-8F46-6CD0F1B59778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -223,6 +223,12 @@
   </si>
   <si>
     <t>Front End Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Structure </t>
+  </si>
+  <si>
+    <t>Database Design</t>
   </si>
 </sst>
 </file>
@@ -252,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +274,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEF3C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF59E0B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF06B6D4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -308,20 +326,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -331,11 +342,17 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -346,8 +363,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF06B6D4"/>
+      <color rgb="FF4F46E5"/>
+      <color rgb="FFF59E0B"/>
       <color rgb="FFFEF3C7"/>
-      <color rgb="FF4F46E5"/>
     </mruColors>
   </colors>
   <extLst>
@@ -658,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4252512-BC7E-4EBC-96E2-ED82A59FCED7}">
-  <dimension ref="E4:H16"/>
+  <dimension ref="G8:H16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
@@ -667,78 +686,75 @@
     <col min="8" max="8" width="29.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="E4" s="2"/>
-    </row>
-    <row r="8" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G8" s="4" t="s">
+    <row r="8" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G9" s="3" t="s">
+    <row r="9" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G10" s="3" t="s">
+    <row r="10" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G11" s="3" t="s">
+    <row r="11" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G12" s="3" t="s">
+    <row r="12" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G13" s="3" t="s">
+    <row r="13" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G14" s="3" t="s">
+    <row r="14" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G15" s="3" t="s">
+    <row r="15" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="5:8" x14ac:dyDescent="0.3">
-      <c r="G16" s="3" t="s">
+    <row r="16" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="1" t="s">
         <v>40</v>
       </c>
     </row>
@@ -758,168 +774,168 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>39</v>
       </c>
     </row>
@@ -950,64 +966,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="10"/>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="5" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1021,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5CB8FFB-371A-48FE-B0A8-736AABF270A1}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -1032,143 +1048,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="7">
         <v>46189</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="7">
         <v>46190</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="A6" s="3">
         <v>2</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="11">
-        <v>44000</v>
-      </c>
-      <c r="E6" s="11">
-        <v>44000</v>
-      </c>
-      <c r="F6" s="6"/>
+      <c r="D6" s="7">
+        <v>46191</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46191</v>
+      </c>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+      <c r="A7" s="3">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="7">
+        <v>46192</v>
+      </c>
+      <c r="E7" s="7">
+        <v>46193</v>
+      </c>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D8" s="7">
         <v>46193</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E8" s="7">
         <v>46200</v>
       </c>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D9" s="7">
         <v>46201</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E9" s="7">
         <v>46202</v>
       </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63A1A4F-9E1A-45C8-8F46-6CD0F1B59778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB4F1AC-B61D-41EE-A3A3-2B41CE325563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Features" sheetId="2" r:id="rId2"/>
     <sheet name="Open Questions" sheetId="4" r:id="rId3"/>
-    <sheet name="EduFlow TimeLine" sheetId="5" r:id="rId4"/>
+    <sheet name="Color Theme " sheetId="6" r:id="rId4"/>
+    <sheet name="EduFlow TimeLine" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="130">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -84,9 +85,6 @@
     <t xml:space="preserve">Features </t>
   </si>
   <si>
-    <t xml:space="preserve">Phase </t>
-  </si>
-  <si>
     <t xml:space="preserve">Status </t>
   </si>
   <si>
@@ -192,43 +190,235 @@
     <t>S.No</t>
   </si>
   <si>
-    <t xml:space="preserve">Task </t>
-  </si>
-  <si>
     <t>Start Date</t>
   </si>
   <si>
-    <t xml:space="preserve">End Date </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creating Functional Requirement For the Project </t>
-  </si>
-  <si>
     <t>Requirement Phase</t>
   </si>
   <si>
     <t xml:space="preserve">EduFlow AI TimeLine </t>
   </si>
   <si>
-    <t xml:space="preserve">Rough Sketching of the project workflow </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI / UX Design using Google Stitch and Figma </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Designing Phase </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finalize the design of the project </t>
-  </si>
-  <si>
-    <t>Front End Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Structure </t>
-  </si>
-  <si>
     <t>Database Design</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Hex</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Indigo</t>
+  </si>
+  <si>
+    <t>#4F46E5</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>Cyan</t>
+  </si>
+  <si>
+    <t>#06B6D4</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>#22C55E</t>
+  </si>
+  <si>
+    <t>Warning</t>
+  </si>
+  <si>
+    <t>Amber</t>
+  </si>
+  <si>
+    <t>#F59E0B</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>Light Gray</t>
+  </si>
+  <si>
+    <t>#F8FAFC</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>Dark Slate</t>
+  </si>
+  <si>
+    <t>#0F172A</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Cover Title</t>
+  </si>
+  <si>
+    <t>Main Headings (H1)</t>
+  </si>
+  <si>
+    <t>Sub Headings (H2)</t>
+  </si>
+  <si>
+    <t>Normal Text</t>
+  </si>
+  <si>
+    <t>Table Headers</t>
+  </si>
+  <si>
+    <t>Table Header Text</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>#FFFFFF</t>
+  </si>
+  <si>
+    <t>Table Borders</t>
+  </si>
+  <si>
+    <t>Gray</t>
+  </si>
+  <si>
+    <t>#CBD5E1</t>
+  </si>
+  <si>
+    <t>Notes / Future Enhancements</t>
+  </si>
+  <si>
+    <t>Page Background</t>
+  </si>
+  <si>
+    <t>Primary Heading      : #4F46E5</t>
+  </si>
+  <si>
+    <t>Sub Heading          : #06B6D4</t>
+  </si>
+  <si>
+    <t>Body Text            : #0F172A</t>
+  </si>
+  <si>
+    <t>Table Header         : #4F46E5</t>
+  </si>
+  <si>
+    <t>Table Border         : #CBD5E1</t>
+  </si>
+  <si>
+    <t>Future Enhancements  : #F59E0B</t>
+  </si>
+  <si>
+    <t>Background           : #FFFFFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EduFlow AI Phase 1 TimeLine </t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Creating Functional Requirements for the Project</t>
+  </si>
+  <si>
+    <t>Rough Sketching of the Project Workflow</t>
+  </si>
+  <si>
+    <t>Database Structure Design</t>
+  </si>
+  <si>
+    <t>UI / UX Design using Google Stitch and Figma</t>
+  </si>
+  <si>
+    <t>Designing Phase</t>
+  </si>
+  <si>
+    <t>Finalize the Project Design</t>
+  </si>
+  <si>
+    <t>Frontend Project Setup (React + Routing)</t>
+  </si>
+  <si>
+    <t>Frontend Development</t>
+  </si>
+  <si>
+    <t>Authentication Screens (Login, Register, Forgot Password)</t>
+  </si>
+  <si>
+    <t>Dashboard, Goals, Tasks and Analytics UI</t>
+  </si>
+  <si>
+    <t>Profile Management and Calendar View UI</t>
+  </si>
+  <si>
+    <t>Backend Project Setup (.NET Core 8 + Architecture)</t>
+  </si>
+  <si>
+    <t>Backend Development</t>
+  </si>
+  <si>
+    <t>Authentication APIs (Login, Register, Forgot Password)</t>
+  </si>
+  <si>
+    <t>Goal Management, Task Management and User Profile APIs</t>
+  </si>
+  <si>
+    <t>Planner Engine V1 and Schedule Generation</t>
+  </si>
+  <si>
+    <t>Core Development</t>
+  </si>
+  <si>
+    <t>Dashboard Integration and Calendar Integration</t>
+  </si>
+  <si>
+    <t>Integration Phase</t>
+  </si>
+  <si>
+    <t>Testing and Bug Fixing</t>
+  </si>
+  <si>
+    <t>Testing Phase</t>
+  </si>
+  <si>
+    <t>Total Tasks</t>
+  </si>
+  <si>
+    <t>Completion %</t>
   </si>
 </sst>
 </file>
@@ -258,7 +448,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -289,8 +479,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -322,11 +542,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -342,18 +577,47 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -363,10 +627,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFEF3C7"/>
+      <color rgb="FFF59E0B"/>
       <color rgb="FF06B6D4"/>
       <color rgb="FF4F46E5"/>
-      <color rgb="FFF59E0B"/>
-      <color rgb="FFFEF3C7"/>
     </mruColors>
   </colors>
   <extLst>
@@ -755,7 +1019,7 @@
         <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -774,169 +1038,169 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="A1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -966,65 +1230,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="9"/>
+      <c r="A1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1036,172 +1300,640 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED9154C-93DA-44CF-8778-E92970739FE3}">
+  <dimension ref="A2:N11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J10" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L10" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="J11" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5CB8FFB-371A-48FE-B0A8-736AABF270A1}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.6640625" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A1" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="E6" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D7" s="14">
+        <v>46189</v>
+      </c>
+      <c r="E7" s="14">
+        <v>46190</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="H7" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="16">
+        <f>COUNTA(B7:B21)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="14">
+        <v>46191</v>
+      </c>
+      <c r="E8" s="14">
+        <v>46191</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="H8" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="17">
+        <f>COUNTIF(F7:F21,"Completed")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="7">
-        <v>46189</v>
-      </c>
-      <c r="E5" s="7">
-        <v>46190</v>
-      </c>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>2</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="7">
-        <v>46191</v>
-      </c>
-      <c r="E6" s="7">
-        <v>46191</v>
-      </c>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="D9" s="14">
         <v>46192</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E9" s="14">
         <v>46193</v>
       </c>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="F9" s="5"/>
+      <c r="H9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="18">
+        <f>COUNTIF(F7:F21,"In Progress")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="14">
         <v>46193</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E10" s="14">
         <v>46200</v>
       </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="F10" s="5"/>
+      <c r="H10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="19">
+        <f>COUNTIF(F7:F21,Planned)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>5</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="14">
         <v>46201</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E11" s="14">
         <v>46202</v>
       </c>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="5"/>
+      <c r="H11" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" s="20">
+        <f>COUNTIF(F8:F22,"Completed")/COUNTA(B8:B22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="14">
+        <v>46203</v>
+      </c>
+      <c r="E12" s="14">
+        <v>46203</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="14">
+        <v>46204</v>
+      </c>
+      <c r="E13" s="14">
+        <v>46204</v>
+      </c>
+      <c r="F13" s="5"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>8</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="14">
+        <v>46205</v>
+      </c>
+      <c r="E14" s="14">
+        <v>46206</v>
+      </c>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="14">
+        <v>46207</v>
+      </c>
+      <c r="E15" s="14">
+        <v>46207</v>
+      </c>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="14">
+        <v>46208</v>
+      </c>
+      <c r="E16" s="14">
+        <v>46208</v>
+      </c>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>11</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="14">
+        <v>46209</v>
+      </c>
+      <c r="E17" s="14">
+        <v>46209</v>
+      </c>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>12</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="14">
+        <v>46210</v>
+      </c>
+      <c r="E18" s="14">
+        <v>46211</v>
+      </c>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>13</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="14">
+        <v>46212</v>
+      </c>
+      <c r="E19" s="14">
+        <v>46221</v>
+      </c>
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>14</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D20" s="14">
+        <v>46222</v>
+      </c>
+      <c r="E20" s="14">
+        <v>46223</v>
+      </c>
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="14">
+        <v>46224</v>
+      </c>
+      <c r="E21" s="14">
+        <v>46225</v>
+      </c>
+      <c r="F21" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F21" xr:uid="{2BA7D6B5-8642-45FA-AE77-6AD981377E68}">
+      <formula1>"Not Started,Started,Planned,In Progress,Research,Completed,Blocked"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB4F1AC-B61D-41EE-A3A3-2B41CE325563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FED570-FE63-4418-9BA5-DD5279DF1DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="130">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -577,15 +577,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -594,9 +585,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -618,6 +606,18 @@
     </xf>
     <xf numFmtId="9" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1038,16 +1038,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1230,10 +1230,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="20"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -1315,28 +1315,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="8" t="s">
         <v>59</v>
       </c>
       <c r="N2" s="3" t="s">
@@ -1365,7 +1365,7 @@
       <c r="K3" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="9" t="s">
         <v>62</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -1394,7 +1394,7 @@
       <c r="K4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="9" t="s">
         <v>62</v>
       </c>
       <c r="N4" s="3" t="s">
@@ -1423,7 +1423,7 @@
       <c r="K5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="9" t="s">
         <v>65</v>
       </c>
       <c r="N5" s="3" t="s">
@@ -1452,7 +1452,7 @@
       <c r="K6" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="9" t="s">
         <v>77</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -1481,7 +1481,7 @@
       <c r="K7" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="9" t="s">
         <v>62</v>
       </c>
       <c r="N7" s="3" t="s">
@@ -1504,7 +1504,7 @@
       <c r="K8" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="9" t="s">
         <v>90</v>
       </c>
       <c r="N8" s="3" t="s">
@@ -1518,7 +1518,7 @@
       <c r="K9" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="9" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       <c r="K10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="9" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       <c r="K11" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="9" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1566,36 +1566,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
@@ -1616,8 +1616,8 @@
       <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
     </row>
     <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
@@ -1629,17 +1629,19 @@
       <c r="C7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="10">
         <v>46189</v>
       </c>
-      <c r="E7" s="14">
-        <v>46190</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="H7" s="15" t="s">
+      <c r="E7" s="10">
+        <v>46192</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="12">
         <f>COUNTA(B7:B21)</f>
         <v>15</v>
       </c>
@@ -1654,17 +1656,19 @@
       <c r="C8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="14">
-        <v>46191</v>
-      </c>
-      <c r="E8" s="14">
-        <v>46191</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="H8" s="15" t="s">
+      <c r="D8" s="10">
+        <v>46193</v>
+      </c>
+      <c r="E8" s="10">
+        <v>46193</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="13">
         <f>COUNTIF(F7:F21,"Completed")</f>
         <v>0</v>
       </c>
@@ -1679,19 +1683,21 @@
       <c r="C9" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="14">
-        <v>46192</v>
-      </c>
-      <c r="E9" s="14">
-        <v>46193</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="H9" s="15" t="s">
+      <c r="D9" s="10">
+        <v>46194</v>
+      </c>
+      <c r="E9" s="10">
+        <v>46195</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="18">
+      <c r="H9" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I9" s="14">
         <f>COUNTIF(F7:F21,"In Progress")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1704,17 +1710,17 @@
       <c r="C10" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="14">
-        <v>46193</v>
-      </c>
-      <c r="E10" s="14">
+      <c r="D10" s="10">
+        <v>46195</v>
+      </c>
+      <c r="E10" s="10">
         <v>46200</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="15">
         <f>COUNTIF(F7:F21,Planned)</f>
         <v>0</v>
       </c>
@@ -1729,17 +1735,17 @@
       <c r="C11" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="10">
         <v>46201</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="10">
         <v>46202</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="16">
         <f>COUNTIF(F8:F22,"Completed")/COUNTA(B8:B22)</f>
         <v>0</v>
       </c>
@@ -1754,10 +1760,10 @@
       <c r="C12" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="10">
         <v>46203</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="10">
         <v>46203</v>
       </c>
       <c r="F12" s="5"/>
@@ -1772,11 +1778,11 @@
       <c r="C13" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="10">
         <v>46204</v>
       </c>
-      <c r="E13" s="14">
-        <v>46204</v>
+      <c r="E13" s="10">
+        <v>46205</v>
       </c>
       <c r="F13" s="5"/>
     </row>
@@ -1790,11 +1796,11 @@
       <c r="C14" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="14">
-        <v>46205</v>
-      </c>
-      <c r="E14" s="14">
+      <c r="D14" s="10">
         <v>46206</v>
+      </c>
+      <c r="E14" s="10">
+        <v>46208</v>
       </c>
       <c r="F14" s="5"/>
     </row>
@@ -1808,11 +1814,11 @@
       <c r="C15" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="14">
-        <v>46207</v>
-      </c>
-      <c r="E15" s="14">
-        <v>46207</v>
+      <c r="D15" s="10">
+        <v>46209</v>
+      </c>
+      <c r="E15" s="10">
+        <v>46210</v>
       </c>
       <c r="F15" s="5"/>
     </row>
@@ -1826,11 +1832,11 @@
       <c r="C16" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="14">
-        <v>46208</v>
-      </c>
-      <c r="E16" s="14">
-        <v>46208</v>
+      <c r="D16" s="10">
+        <v>46211</v>
+      </c>
+      <c r="E16" s="10">
+        <v>46211</v>
       </c>
       <c r="F16" s="5"/>
     </row>
@@ -1844,11 +1850,11 @@
       <c r="C17" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="14">
-        <v>46209</v>
-      </c>
-      <c r="E17" s="14">
-        <v>46209</v>
+      <c r="D17" s="10">
+        <v>46212</v>
+      </c>
+      <c r="E17" s="10">
+        <v>46215</v>
       </c>
       <c r="F17" s="5"/>
     </row>
@@ -1862,11 +1868,11 @@
       <c r="C18" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="14">
-        <v>46210</v>
-      </c>
-      <c r="E18" s="14">
-        <v>46211</v>
+      <c r="D18" s="10">
+        <v>46216</v>
+      </c>
+      <c r="E18" s="10">
+        <v>46221</v>
       </c>
       <c r="F18" s="5"/>
     </row>
@@ -1880,11 +1886,11 @@
       <c r="C19" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="14">
-        <v>46212</v>
-      </c>
-      <c r="E19" s="14">
-        <v>46221</v>
+      <c r="D19" s="10">
+        <v>46222</v>
+      </c>
+      <c r="E19" s="10">
+        <v>46230</v>
       </c>
       <c r="F19" s="5"/>
     </row>
@@ -1898,11 +1904,11 @@
       <c r="C20" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="14">
-        <v>46222</v>
-      </c>
-      <c r="E20" s="14">
-        <v>46223</v>
+      <c r="D20" s="10">
+        <v>46231</v>
+      </c>
+      <c r="E20" s="10">
+        <v>46239</v>
       </c>
       <c r="F20" s="5"/>
     </row>
@@ -1916,11 +1922,11 @@
       <c r="C21" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="14">
-        <v>46224</v>
-      </c>
-      <c r="E21" s="14">
-        <v>46225</v>
+      <c r="D21" s="10">
+        <v>46240</v>
+      </c>
+      <c r="E21" s="10">
+        <v>46242</v>
       </c>
       <c r="F21" s="5"/>
     </row>

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FED570-FE63-4418-9BA5-DD5279DF1DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C642769-57FF-4B04-9B50-AF344200B4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="132">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -419,6 +419,13 @@
   </si>
   <si>
     <t>Completion %</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Function Requirement 
+is been documented for the phase 1 only </t>
   </si>
 </sst>
 </file>
@@ -561,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -619,14 +626,493 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF00FFFF"/>
       <color rgb="FFFEF3C7"/>
       <color rgb="FFF59E0B"/>
       <color rgb="FF06B6D4"/>
@@ -1558,11 +2044,13 @@
     <col min="2" max="2" width="50.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.6640625" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
@@ -1587,7 +2075,7 @@
       <c r="Q1" s="17"/>
       <c r="R1" s="17"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="18" t="s">
         <v>103</v>
       </c>
@@ -1596,6 +2084,7 @@
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
     </row>
     <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
@@ -1616,10 +2105,20 @@
       <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="G6" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L6" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="M6" s="12">
+        <f>COUNTA(B7:B21)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -1636,14 +2135,17 @@
         <v>46192</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="I7" s="12">
-        <f>COUNTA(B7:B21)</f>
-        <v>15</v>
+        <v>78</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="13">
+        <f>COUNTIF(F7:F21,"Completed")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1665,12 +2167,13 @@
       <c r="F8" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="13">
-        <f>COUNTIF(F7:F21,"Completed")</f>
-        <v>0</v>
+      <c r="G8" s="22"/>
+      <c r="L8" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" s="14">
+        <f>COUNTIF(F7:F21,"In Progress")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1690,14 +2193,15 @@
         <v>46195</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="14">
-        <f>COUNTIF(F7:F21,"In Progress")</f>
-        <v>3</v>
+        <v>78</v>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="L9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9" s="15">
+        <f>COUNTIF(F7:F21,Planned)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1717,15 +2221,16 @@
         <v>46200</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="H10" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="15">
-        <f>COUNTIF(F7:F21,Planned)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G10" s="22"/>
+      <c r="L10" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="M10" s="16">
+        <f>COUNTIF(F8:F22,"Completed")/COUNTA(B8:B22)</f>
+        <v>7.1428571428571425E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>5</v>
       </c>
@@ -1742,13 +2247,7 @@
         <v>46202</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="H11" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I11" s="16">
-        <f>COUNTIF(F8:F22,"Completed")/COUNTA(B8:B22)</f>
-        <v>0</v>
-      </c>
+      <c r="G11" s="22"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
@@ -1767,6 +2266,7 @@
         <v>46203</v>
       </c>
       <c r="F12" s="5"/>
+      <c r="G12" s="22"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
@@ -1785,6 +2285,7 @@
         <v>46205</v>
       </c>
       <c r="F13" s="5"/>
+      <c r="G13" s="22"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -1803,6 +2304,7 @@
         <v>46208</v>
       </c>
       <c r="F14" s="5"/>
+      <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
@@ -1821,6 +2323,7 @@
         <v>46210</v>
       </c>
       <c r="F15" s="5"/>
+      <c r="G15" s="22"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
@@ -1839,8 +2342,9 @@
         <v>46211</v>
       </c>
       <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="22"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>11</v>
       </c>
@@ -1857,8 +2361,9 @@
         <v>46215</v>
       </c>
       <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="22"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>12</v>
       </c>
@@ -1875,8 +2380,9 @@
         <v>46221</v>
       </c>
       <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="22"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>13</v>
       </c>
@@ -1893,8 +2399,9 @@
         <v>46230</v>
       </c>
       <c r="F19" s="5"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="22"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>14</v>
       </c>
@@ -1911,8 +2418,9 @@
         <v>46239</v>
       </c>
       <c r="F20" s="5"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="22"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>15</v>
       </c>
@@ -1929,12 +2437,36 @@
         <v>46242</v>
       </c>
       <c r="F21" s="5"/>
+      <c r="G21" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="F7:F21">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+      <formula>"In Progress"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+      <formula>"Not Started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+      <formula>"Started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
+      <formula>"Planned"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+      <formula>"Research"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"Blocked"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F21" xr:uid="{2BA7D6B5-8642-45FA-AE77-6AD981377E68}">
       <formula1>"Not Started,Started,Planned,In Progress,Research,Completed,Blocked"</formula1>

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C642769-57FF-4B04-9B50-AF344200B4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A479E1E4-E1AF-4291-8D0E-9BF629923750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -568,7 +568,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -614,6 +614,9 @@
     <xf numFmtId="9" fontId="1" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -626,444 +629,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="43">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00FFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <b/>
@@ -1093,7 +663,7 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1104,7 +674,40 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="9"/>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1524,16 +1127,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1716,10 +1319,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -2031,6 +1634,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2054,37 +1658,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
     </row>
     <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
@@ -2137,7 +1741,7 @@
       <c r="F7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="17" t="s">
         <v>131</v>
       </c>
       <c r="L7" s="11" t="s">
@@ -2159,15 +1763,15 @@
         <v>54</v>
       </c>
       <c r="D8" s="10">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="E8" s="10">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="22"/>
+      <c r="G8" s="3"/>
       <c r="L8" s="11" t="s">
         <v>79</v>
       </c>
@@ -2195,7 +1799,7 @@
       <c r="F9" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="3"/>
       <c r="L9" s="11" t="s">
         <v>36</v>
       </c>
@@ -2215,13 +1819,13 @@
         <v>111</v>
       </c>
       <c r="D10" s="10">
-        <v>46195</v>
+        <v>46201</v>
       </c>
       <c r="E10" s="10">
-        <v>46200</v>
+        <v>46205</v>
       </c>
       <c r="F10" s="5"/>
-      <c r="G10" s="22"/>
+      <c r="G10" s="3"/>
       <c r="L10" s="11" t="s">
         <v>129</v>
       </c>
@@ -2241,13 +1845,13 @@
         <v>111</v>
       </c>
       <c r="D11" s="10">
-        <v>46201</v>
+        <v>46205</v>
       </c>
       <c r="E11" s="10">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="F11" s="5"/>
-      <c r="G11" s="22"/>
+      <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
@@ -2260,13 +1864,13 @@
         <v>114</v>
       </c>
       <c r="D12" s="10">
-        <v>46203</v>
+        <v>46206</v>
       </c>
       <c r="E12" s="10">
-        <v>46203</v>
+        <v>46207</v>
       </c>
       <c r="F12" s="5"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
@@ -2279,13 +1883,13 @@
         <v>114</v>
       </c>
       <c r="D13" s="10">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="E13" s="10">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="22"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -2298,13 +1902,13 @@
         <v>114</v>
       </c>
       <c r="D14" s="10">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="E14" s="10">
-        <v>46208</v>
+        <v>46210</v>
       </c>
       <c r="F14" s="5"/>
-      <c r="G14" s="22"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
@@ -2317,13 +1921,13 @@
         <v>114</v>
       </c>
       <c r="D15" s="10">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="E15" s="10">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="22"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
@@ -2336,13 +1940,13 @@
         <v>119</v>
       </c>
       <c r="D16" s="10">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="E16" s="10">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="22"/>
+      <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
@@ -2355,13 +1959,13 @@
         <v>119</v>
       </c>
       <c r="D17" s="10">
-        <v>46212</v>
+        <v>46214</v>
       </c>
       <c r="E17" s="10">
         <v>46215</v>
       </c>
       <c r="F17" s="5"/>
-      <c r="G17" s="22"/>
+      <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
@@ -2380,7 +1984,7 @@
         <v>46221</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="22"/>
+      <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
@@ -2399,7 +2003,7 @@
         <v>46230</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="22"/>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
@@ -2418,7 +2022,7 @@
         <v>46239</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="22"/>
+      <c r="G20" s="3"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
@@ -2437,7 +2041,7 @@
         <v>46242</v>
       </c>
       <c r="F21" s="5"/>
-      <c r="G21" s="22"/>
+      <c r="G21" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2445,26 +2049,26 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <conditionalFormatting sqref="F7:F21">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
-      <formula>"Completed"</formula>
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+      <formula>"Research"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+      <formula>"Planned"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>"Started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
+      <formula>"Not Started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
-      <formula>"Not Started"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
-      <formula>"Started"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
-      <formula>"Planned"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
-      <formula>"Research"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"Blocked"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+      <formula>"Completed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A479E1E4-E1AF-4291-8D0E-9BF629923750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0885FAB1-9EA8-47B3-AEAE-EEB05076DA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -617,16 +617,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1127,16 +1127,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1319,10 +1319,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -1658,37 +1658,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="18"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
     </row>
     <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="M7" s="13">
         <f>COUNTIF(F7:F21,"Completed")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1769,7 +1769,7 @@
         <v>46200</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G8" s="3"/>
       <c r="L8" s="11" t="s">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="M8" s="14">
         <f>COUNTIF(F7:F21,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1819,10 +1819,10 @@
         <v>111</v>
       </c>
       <c r="D10" s="10">
-        <v>46201</v>
+        <v>46205</v>
       </c>
       <c r="E10" s="10">
-        <v>46205</v>
+        <v>46212</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="3"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="M10" s="16">
         <f>COUNTIF(F8:F22,"Completed")/COUNTA(B8:B22)</f>
-        <v>7.1428571428571425E-2</v>
+        <v>0.14285714285714285</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -1845,10 +1845,10 @@
         <v>111</v>
       </c>
       <c r="D11" s="10">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="E11" s="10">
-        <v>46205</v>
+        <v>46213</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="3"/>
@@ -1864,10 +1864,10 @@
         <v>114</v>
       </c>
       <c r="D12" s="10">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="E12" s="10">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="3"/>
@@ -1883,10 +1883,10 @@
         <v>114</v>
       </c>
       <c r="D13" s="10">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="E13" s="10">
-        <v>46209</v>
+        <v>46215</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="3"/>
@@ -1902,10 +1902,10 @@
         <v>114</v>
       </c>
       <c r="D14" s="10">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="E14" s="10">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="3"/>
@@ -1921,10 +1921,10 @@
         <v>114</v>
       </c>
       <c r="D15" s="10">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="E15" s="10">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="3"/>
@@ -1940,10 +1940,10 @@
         <v>119</v>
       </c>
       <c r="D16" s="10">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="E16" s="10">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="3"/>
@@ -1959,10 +1959,10 @@
         <v>119</v>
       </c>
       <c r="D17" s="10">
-        <v>46214</v>
+        <v>46219</v>
       </c>
       <c r="E17" s="10">
-        <v>46215</v>
+        <v>46220</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="3"/>
@@ -1978,10 +1978,10 @@
         <v>119</v>
       </c>
       <c r="D18" s="10">
-        <v>46216</v>
+        <v>46221</v>
       </c>
       <c r="E18" s="10">
-        <v>46221</v>
+        <v>46225</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="3"/>
@@ -1997,10 +1997,10 @@
         <v>123</v>
       </c>
       <c r="D19" s="10">
-        <v>46222</v>
+        <v>46226</v>
       </c>
       <c r="E19" s="10">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="3"/>
@@ -2016,7 +2016,7 @@
         <v>125</v>
       </c>
       <c r="D20" s="10">
-        <v>46231</v>
+        <v>46235</v>
       </c>
       <c r="E20" s="10">
         <v>46239</v>

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0885FAB1-9EA8-47B3-AEAE-EEB05076DA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -617,16 +617,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1127,16 +1127,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -1319,10 +1319,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
@@ -1658,37 +1658,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
     </row>
     <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
     </row>
     <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0885FAB1-9EA8-47B3-AEAE-EEB05076DA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FF4870-1D36-4254-935C-67A6BB084CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="132">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -1824,7 +1824,9 @@
       <c r="E10" s="10">
         <v>46212</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="L10" s="11" t="s">
         <v>129</v>
@@ -1850,7 +1852,9 @@
       <c r="E11" s="10">
         <v>46213</v>
       </c>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9FF4870-1D36-4254-935C-67A6BB084CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3551790B-5B1D-422E-A81C-5E385B8594A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="133">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -365,9 +365,6 @@
   </si>
   <si>
     <t>Designing Phase</t>
-  </si>
-  <si>
-    <t>Finalize the Project Design</t>
   </si>
   <si>
     <t>Frontend Project Setup (React + Routing)</t>
@@ -426,6 +423,12 @@
   <si>
     <t xml:space="preserve">The Function Requirement 
 is been documented for the phase 1 only </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB setup </t>
+  </si>
+  <si>
+    <t>Started</t>
   </si>
 </sst>
 </file>
@@ -1710,12 +1713,12 @@
         <v>13</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M6" s="12">
         <f>COUNTA(B7:B21)</f>
@@ -1742,14 +1745,14 @@
         <v>78</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L7" s="11" t="s">
         <v>78</v>
       </c>
       <c r="M7" s="13">
         <f>COUNTIF(F7:F21,"Completed")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1777,7 +1780,7 @@
       </c>
       <c r="M8" s="14">
         <f>COUNTIF(F7:F21,"In Progress")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1825,15 +1828,15 @@
         <v>46212</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="G10" s="3"/>
       <c r="L10" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M10" s="16">
         <f>COUNTIF(F8:F22,"Completed")/COUNTA(B8:B22)</f>
-        <v>0.14285714285714285</v>
+        <v>0.21428571428571427</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -1841,7 +1844,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>111</v>
@@ -1853,7 +1856,7 @@
         <v>46213</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="G11" s="3"/>
     </row>
@@ -1862,10 +1865,10 @@
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>114</v>
       </c>
       <c r="D12" s="10">
         <v>46213</v>
@@ -1873,7 +1876,9 @@
       <c r="E12" s="10">
         <v>46213</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -1881,10 +1886,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D13" s="10">
         <v>46214</v>
@@ -1892,7 +1897,9 @@
       <c r="E13" s="10">
         <v>46215</v>
       </c>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>132</v>
+      </c>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -1900,10 +1907,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14" s="10">
         <v>46216</v>
@@ -1919,10 +1926,10 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D15" s="10">
         <v>46217</v>
@@ -1938,10 +1945,10 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>118</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>119</v>
       </c>
       <c r="D16" s="10">
         <v>46218</v>
@@ -1957,10 +1964,10 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="10">
         <v>46219</v>
@@ -1976,10 +1983,10 @@
         <v>12</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D18" s="10">
         <v>46221</v>
@@ -1995,10 +2002,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="D19" s="10">
         <v>46226</v>
@@ -2014,10 +2021,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="D20" s="10">
         <v>46235</v>
@@ -2033,10 +2040,10 @@
         <v>15</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="D21" s="10">
         <v>46240</v>

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3551790B-5B1D-422E-A81C-5E385B8594A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7FF302-261F-4C2B-BE52-E550EEE0E00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="132">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -426,9 +426,6 @@
   </si>
   <si>
     <t xml:space="preserve">DB setup </t>
-  </si>
-  <si>
-    <t>Started</t>
   </si>
 </sst>
 </file>
@@ -1780,7 +1777,7 @@
       </c>
       <c r="M8" s="14">
         <f>COUNTIF(F7:F21,"In Progress")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1898,7 +1895,7 @@
         <v>46215</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="G13" s="3"/>
     </row>

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7FF302-261F-4C2B-BE52-E550EEE0E00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218A2580-AB03-4C66-A029-DC3ADA479AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
+    <workbookView xWindow="3864" yWindow="1176" windowWidth="17280" windowHeight="8880" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="134">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -380,9 +380,6 @@
   </si>
   <si>
     <t>Profile Management and Calendar View UI</t>
-  </si>
-  <si>
-    <t>Backend Project Setup (.NET Core 8 + Architecture)</t>
   </si>
   <si>
     <t>Backend Development</t>
@@ -426,6 +423,15 @@
   </si>
   <si>
     <t xml:space="preserve">DB setup </t>
+  </si>
+  <si>
+    <t>Backend Project Setup (.NET Core 10, Architecture)</t>
+  </si>
+  <si>
+    <t>AI Phase</t>
+  </si>
+  <si>
+    <t>AI - Implementation of EduFlow AI and integration</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1647,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5CB8FFB-371A-48FE-B0A8-736AABF270A1}">
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
@@ -1710,16 +1716,16 @@
         <v>13</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M6" s="12">
-        <f>COUNTA(B7:B21)</f>
-        <v>15</v>
+        <f>COUNTA(B7:B22)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1742,14 +1748,14 @@
         <v>78</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L7" s="11" t="s">
         <v>78</v>
       </c>
       <c r="M7" s="13">
-        <f>COUNTIF(F7:F21,"Completed")</f>
-        <v>4</v>
+        <f>COUNTIF(F7:F22,"Completed")</f>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1776,8 +1782,8 @@
         <v>79</v>
       </c>
       <c r="M8" s="14">
-        <f>COUNTIF(F7:F21,"In Progress")</f>
-        <v>3</v>
+        <f>COUNTIF(F7:F22,"In Progress")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1804,7 +1810,7 @@
         <v>36</v>
       </c>
       <c r="M9" s="15">
-        <f>COUNTIF(F7:F21,Planned)</f>
+        <f>COUNTIF(F7:F22,Planned)</f>
         <v>0</v>
       </c>
     </row>
@@ -1829,11 +1835,11 @@
       </c>
       <c r="G10" s="3"/>
       <c r="L10" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M10" s="16">
-        <f>COUNTIF(F8:F22,"Completed")/COUNTA(B8:B22)</f>
-        <v>0.21428571428571427</v>
+        <f>COUNTIF(F8:F23,"Completed")/COUNTA(B8:B23)</f>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -1841,7 +1847,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>111</v>
@@ -1853,7 +1859,7 @@
         <v>46213</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G11" s="3"/>
     </row>
@@ -1895,7 +1901,7 @@
         <v>46215</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3"/>
     </row>
@@ -1913,9 +1919,11 @@
         <v>46216</v>
       </c>
       <c r="E14" s="10">
-        <v>46217</v>
-      </c>
-      <c r="F14" s="5"/>
+        <v>46219</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>79</v>
+      </c>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -1929,10 +1937,10 @@
         <v>113</v>
       </c>
       <c r="D15" s="10">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="E15" s="10">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="3"/>
@@ -1942,18 +1950,20 @@
         <v>10</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="D16" s="10">
-        <v>46218</v>
+        <v>46215</v>
       </c>
       <c r="E16" s="10">
-        <v>46218</v>
-      </c>
-      <c r="F16" s="5"/>
+        <v>46215</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1961,16 +1971,16 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D17" s="10">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="E17" s="10">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="3"/>
@@ -1980,13 +1990,13 @@
         <v>12</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D18" s="10">
-        <v>46221</v>
+        <v>46224</v>
       </c>
       <c r="E18" s="10">
         <v>46225</v>
@@ -1999,10 +2009,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="D19" s="10">
         <v>46226</v>
@@ -2018,10 +2028,10 @@
         <v>14</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="D20" s="10">
         <v>46235</v>
@@ -2037,26 +2047,45 @@
         <v>15</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D21" s="10">
         <v>46240</v>
       </c>
       <c r="E21" s="10">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>16</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="10">
+        <v>46244</v>
+      </c>
+      <c r="E22" s="10">
+        <v>46245</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
-  <conditionalFormatting sqref="F7:F21">
+  <conditionalFormatting sqref="F7:F22">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
@@ -2080,7 +2109,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F21" xr:uid="{2BA7D6B5-8642-45FA-AE77-6AD981377E68}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F22" xr:uid="{2BA7D6B5-8642-45FA-AE77-6AD981377E68}">
       <formula1>"Not Started,Started,Planned,In Progress,Research,Completed,Blocked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/EduFlow AI Details.xlsx
+++ b/docs/EduFlow AI Details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Projects\EduFlowAI\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218A2580-AB03-4C66-A029-DC3ADA479AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{906CF3B7-43CD-4030-8E9F-0E87571E34F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3864" yWindow="1176" windowWidth="17280" windowHeight="8880" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{92BD4C14-6350-41A2-989D-BE19952A9F2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="135">
   <si>
     <t>EduFlow AI</t>
   </si>
@@ -432,6 +432,9 @@
   </si>
   <si>
     <t>AI - Implementation of EduFlow AI and integration</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1758,7 @@
       </c>
       <c r="M7" s="13">
         <f>COUNTIF(F7:F22,"Completed")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1839,7 +1842,7 @@
       </c>
       <c r="M10" s="16">
         <f>COUNTIF(F8:F23,"Completed")/COUNTA(B8:B23)</f>
-        <v>0.4</v>
+        <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -1861,7 +1864,9 @@
       <c r="F11" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
@@ -1942,7 +1947,9 @@
       <c r="E15" s="10">
         <v>46222</v>
       </c>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -1982,7 +1989,9 @@
       <c r="E17" s="10">
         <v>46223</v>
       </c>
-      <c r="F17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
